--- a/data/trans_orig/IP04D$individual-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$individual-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25603</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43501</t>
+          <t>42949</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,82 +747,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>31,04%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>45403</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>35706</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>55911</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>29,35%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>23,08%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>36,15%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>79294</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>67113</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>92105</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>27,06%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>22,9%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>31,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>45403</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>35756</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>54743</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>29,35%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>23,12%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>35,39%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>79294</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>66396</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>93341</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>27,06%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>22,66%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94887</t>
+          <t>95439</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112785</t>
+          <t>112889</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,82 +860,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>68,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>81,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>109281</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>98773</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>118978</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>70,65%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>63,85%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>76,92%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>213778</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>200967</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>225959</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>72,94%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>68,57%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>81,5%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>109281</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>99941</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>118928</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>70,65%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>64,61%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>76,88%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>213778</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>199731</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>226676</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>72,94%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>68,15%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,1%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47750</t>
+          <t>49216</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68130</t>
+          <t>69636</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51691</t>
+          <t>51759</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73677</t>
+          <t>73919</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>106523</t>
+          <t>108774</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137664</t>
+          <t>138121</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>136889</t>
+          <t>135383</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>157269</t>
+          <t>155803</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>150158</t>
+          <t>149916</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>172144</t>
+          <t>172076</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>291190</t>
+          <t>290733</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>322331</t>
+          <t>320080</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,64%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25746</t>
+          <t>25665</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41362</t>
+          <t>41987</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35515</t>
+          <t>36203</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54001</t>
+          <t>53948</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65419</t>
+          <t>65449</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88906</t>
+          <t>90848</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>113389</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129630</t>
+          <t>129711</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111309</t>
+          <t>111362</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129795</t>
+          <t>129107</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>231780</t>
+          <t>229838</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>255267</t>
+          <t>255237</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,59%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62598</t>
+          <t>62646</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85978</t>
+          <t>86485</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74535</t>
+          <t>74177</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98422</t>
+          <t>98750</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>143383</t>
+          <t>142834</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177666</t>
+          <t>177136</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,39%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>123532</t>
+          <t>123025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>146912</t>
+          <t>146864</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109974</t>
+          <t>109646</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133861</t>
+          <t>134219</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>240240</t>
+          <t>240770</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>274523</t>
+          <t>275072</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,82%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>181701</t>
+          <t>179896</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>221031</t>
+          <t>219776</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>217052</t>
+          <t>217360</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>258778</t>
+          <t>259166</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>407801</t>
+          <t>409122</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>466932</t>
+          <t>467887</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>487261</t>
+          <t>488516</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>526591</t>
+          <t>528396</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>493447</t>
+          <t>493059</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>535173</t>
+          <t>534865</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>993585</t>
+          <t>992630</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1052716</t>
+          <t>1051395</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,99%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33244</t>
+          <t>32168</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51331</t>
+          <t>50535</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>26656</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43684</t>
+          <t>44297</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63773</t>
+          <t>65160</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88825</t>
+          <t>91939</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81541</t>
+          <t>82337</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99628</t>
+          <t>100704</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>104392</t>
+          <t>103779</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>121421</t>
+          <t>121420</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>192123</t>
+          <t>189009</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>217175</t>
+          <t>215788</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>76,81%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53014</t>
+          <t>54401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73570</t>
+          <t>73483</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55786</t>
+          <t>55684</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77609</t>
+          <t>78364</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>114294</t>
+          <t>115174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>142895</t>
+          <t>145938</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>132409</t>
+          <t>132496</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>152965</t>
+          <t>151578</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>146079</t>
+          <t>145324</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>167902</t>
+          <t>168004</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>286772</t>
+          <t>283729</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>315373</t>
+          <t>314493</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,19%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47446</t>
+          <t>47243</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65397</t>
+          <t>65827</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46961</t>
+          <t>47358</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67289</t>
+          <t>67550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98458</t>
+          <t>98262</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126891</t>
+          <t>125943</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,12%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90600</t>
+          <t>90170</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108551</t>
+          <t>108754</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>98625</t>
+          <t>98364</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>118953</t>
+          <t>118556</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>195020</t>
+          <t>195968</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>223453</t>
+          <t>223649</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,48%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49428</t>
+          <t>51681</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72886</t>
+          <t>73558</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44810</t>
+          <t>43827</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>64405</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102537</t>
+          <t>100581</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132983</t>
+          <t>131265</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132446</t>
+          <t>131774</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>155904</t>
+          <t>153651</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137963</t>
+          <t>137928</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157523</t>
+          <t>158506</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>274682</t>
+          <t>276400</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>305128</t>
+          <t>307084</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>75,33%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>202173</t>
+          <t>203027</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>242461</t>
+          <t>242223</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>190319</t>
+          <t>193406</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>232392</t>
+          <t>234009</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>409889</t>
+          <t>405192</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>465742</t>
+          <t>463161</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>457720</t>
+          <t>457958</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>498008</t>
+          <t>497154</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>507619</t>
+          <t>506002</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>549692</t>
+          <t>546605</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>974450</t>
+          <t>977031</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1030303</t>
+          <t>1035000</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,87%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14198</t>
+          <t>14119</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28680</t>
+          <t>28925</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28011</t>
+          <t>27090</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64480</t>
+          <t>66005</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45928</t>
+          <t>46921</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89137</t>
+          <t>90895</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>35,27%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88600</t>
+          <t>88355</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103082</t>
+          <t>103161</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75932</t>
+          <t>74407</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112401</t>
+          <t>113322</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>168556</t>
+          <t>166798</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>211765</t>
+          <t>210772</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,79%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21506</t>
+          <t>21634</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38854</t>
+          <t>39346</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33805</t>
+          <t>33944</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57473</t>
+          <t>57464</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60321</t>
+          <t>61432</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89692</t>
+          <t>91757</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>150659</t>
+          <t>150167</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>168007</t>
+          <t>167879</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>196855</t>
+          <t>196864</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>220523</t>
+          <t>220384</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>354149</t>
+          <t>352084</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>383520</t>
+          <t>382409</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,16%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13375</t>
+          <t>13493</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15160</t>
+          <t>13939</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36199</t>
+          <t>35972</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20133</t>
+          <t>21066</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46063</t>
+          <t>47643</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>177026</t>
+          <t>176908</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>186867</t>
+          <t>186806</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149087</t>
+          <t>149314</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>170126</t>
+          <t>171347</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>329624</t>
+          <t>328044</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>355554</t>
+          <t>354621</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40122</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60183</t>
+          <t>59611</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38239</t>
+          <t>38058</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60126</t>
+          <t>60058</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83613</t>
+          <t>84547</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111975</t>
+          <t>114585</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>107779</t>
+          <t>108351</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>127840</t>
+          <t>129104</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>120169</t>
+          <t>120237</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>142056</t>
+          <t>142237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>236282</t>
+          <t>233672</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>264644</t>
+          <t>263710</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,72%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>87393</t>
+          <t>89346</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123999</t>
+          <t>126675</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>134069</t>
+          <t>134546</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>191362</t>
+          <t>189991</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>234280</t>
+          <t>232576</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>303437</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>541157</t>
+          <t>538481</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>577763</t>
+          <t>575810</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>568960</t>
+          <t>570331</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>626253</t>
+          <t>625776</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1122040</t>
+          <t>1124560</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1191197</t>
+          <t>1192901</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04D$individual-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$individual-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>45403</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>36435</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>55751</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>29,35%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>23,55%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>36,04%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>33891</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25499</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>42949</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>25427</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>42904</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>24,49%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,43%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>31,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>45403</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>35706</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>55911</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>29,35%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67113</t>
+          <t>68326</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92105</t>
+          <t>92138</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>109281</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>98933</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>118249</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>70,65%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>63,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>76,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>104497</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>95439</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>112889</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>95484</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>112961</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>75,51%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>68,96%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>81,57%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>109281</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>98773</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>118978</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>70,65%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>200967</t>
+          <t>200934</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>225959</t>
+          <t>224746</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>76,69%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138388</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138388</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138388</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>62435</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>51406</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>73498</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>27,89%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>22,97%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>32,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>58754</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>49216</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>69636</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>48836</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>68861</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>28,66%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>24,01%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>33,97%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>62435</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>51759</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>73919</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>27,89%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108774</t>
+          <t>106662</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>138121</t>
+          <t>137291</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>161400</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>150337</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>172429</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>72,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>67,16%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>77,03%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>146265</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>135383</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>155803</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>136158</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>156183</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>71,34%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>66,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>75,99%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>161400</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>149916</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>172076</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>72,11%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>290733</t>
+          <t>291563</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>320080</t>
+          <t>322192</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>75,13%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205019</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205019</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205019</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>43753</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>35624</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>52971</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>26,47%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>21,55%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>32,04%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>33361</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>25665</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>41987</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>25363</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>41509</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>21,47%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16,52%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>27,02%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>43753</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>36203</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>53948</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>26,47%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65449</t>
+          <t>65676</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90848</t>
+          <t>89536</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>121557</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>112339</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>129686</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>73,53%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>67,96%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>78,45%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>122015</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>113389</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>129711</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>113867</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>130013</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>78,53%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>72,98%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>83,48%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>121557</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>111362</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>129107</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>73,53%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>229838</t>
+          <t>231150</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>255237</t>
+          <t>255010</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,52%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165310</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165310</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165310</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165310</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165310</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165310</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>86430</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>75232</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>98895</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>41,47%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>36,1%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>47,46%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>73902</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>62646</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>86485</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>62476</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>85231</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>35,27%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29,9%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>41,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>86430</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>74177</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>98750</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>41,47%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142834</t>
+          <t>143429</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177136</t>
+          <t>175866</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,08%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>121966</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>109501</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>133164</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>58,53%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>52,54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>63,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>135608</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>123025</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>146864</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>124279</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>147034</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>64,73%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>58,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>70,1%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>121966</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>109646</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>134219</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>58,53%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>240770</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>275072</t>
+          <t>274477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,68%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209510</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209510</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209510</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>238021</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>219149</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>259581</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>31,64%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29,13%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>34,51%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>287</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>199908</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>179896</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>219776</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>180444</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>219171</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>28,22%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25,4%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>31,03%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>238021</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>217360</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>259166</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>31,64%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>409122</t>
+          <t>409018</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>467887</t>
+          <t>467293</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>514204</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>492644</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>533076</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>68,36%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>65,49%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>70,87%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>734</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>508384</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>488516</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>528396</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>489121</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>527848</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>71,78%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>68,97%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>74,6%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>730</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>514204</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>493059</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>534865</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>68,36%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>992630</t>
+          <t>993224</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1051395</t>
+          <t>1051499</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,0%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1021</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1072</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>35089</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26530</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>43751</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>23,7%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>17,92%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>29,55%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>41477</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>32168</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>50535</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>32255</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>51463</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>31,22%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,21%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>38,03%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>35089</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>26656</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>44297</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>23,7%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65160</t>
+          <t>64476</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91939</t>
+          <t>89212</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>112987</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>104325</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>121546</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>76,3%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>70,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>82,08%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>91395</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>82337</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>100704</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>81409</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>100617</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>68,78%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>61,97%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>75,79%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>112987</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>103779</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>121420</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>76,3%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>189009</t>
+          <t>191736</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>215788</t>
+          <t>216472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,05%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>132872</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>132872</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>132872</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>66193</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>56390</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>77379</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>29,59%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>25,21%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>34,59%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>63303</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54401</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>73483</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>53424</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>74681</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>30,73%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>26,41%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>35,68%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>66193</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>55684</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>78364</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>29,59%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115174</t>
+          <t>114543</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>145938</t>
+          <t>145031</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,75%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>157495</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>146309</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>167298</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>70,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>65,41%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>74,79%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>142676</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>132496</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>151578</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>131298</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>152555</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>69,27%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>64,32%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>73,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>157495</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>145324</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>168004</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>70,41%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>283729</t>
+          <t>284636</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>314493</t>
+          <t>315124</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,34%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223688</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223688</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223688</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205979</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205979</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205979</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223688</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223688</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223688</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56231</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>45608</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>66198</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>33,89%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,49%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>39,9%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>56124</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>47243</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>65827</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>46548</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>65126</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>35,98%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>42,2%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>56231</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>47358</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>67550</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>33,89%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98262</t>
+          <t>98068</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125943</t>
+          <t>125666</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,04%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>109683</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>99716</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>120306</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>66,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>60,1%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>72,51%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>99873</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>90170</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>108754</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>90871</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>109449</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>64,02%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>57,8%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>69,72%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>109683</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>98364</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>118556</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>66,11%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>195968</t>
+          <t>196245</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>223649</t>
+          <t>223843</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,54%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165914</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165914</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165914</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165914</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165914</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165914</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>54526</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>45115</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>64953</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>26,95%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>22,3%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>32,1%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>61841</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>51681</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>73558</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>50851</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>72997</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>30,12%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>25,17%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>35,82%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>54526</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>43827</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>64405</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>26,95%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100581</t>
+          <t>102479</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131265</t>
+          <t>132785</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>147807</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>137380</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>157218</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>73,05%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>67,9%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>77,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>143491</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>131774</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>153651</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>132335</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>154481</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>69,88%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>64,18%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>74,83%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>147807</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>137928</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>158506</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>73,05%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>276400</t>
+          <t>274880</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>307084</t>
+          <t>305186</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>74,86%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202333</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202333</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202333</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205332</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205332</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205332</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202333</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202333</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202333</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>212039</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>193026</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>230708</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>28,65%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>26,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>31,18%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>342</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>222745</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>203027</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>242223</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>202777</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>242038</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>31,81%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>34,59%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>212039</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>193406</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>234009</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>28,65%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>405192</t>
+          <t>406858</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>463161</t>
+          <t>464447</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,25%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>527972</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>509303</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>546985</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>71,35%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>68,82%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>73,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>713</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>477436</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>457958</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>497154</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>458143</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>497404</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>68,19%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>65,41%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>71,0%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>752</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>527972</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>506002</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>546605</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>71,35%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>977031</t>
+          <t>975745</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1035000</t>
+          <t>1033334</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,75%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1055</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36220</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>25420</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>57909</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>28,77%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20,19%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>45,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>20571</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14119</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>28925</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17,54%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,04%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>40182</t>
+          <t>20724</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27090</t>
+          <t>14932</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66005</t>
+          <t>28683</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>60753</t>
+          <t>56944</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46921</t>
+          <t>44329</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90895</t>
+          <t>80017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>89686</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>67997</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>100486</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>71,23%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>54,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>79,81%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>96709</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>88355</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>103161</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>82,46%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>75,34%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>87,96%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>100230</t>
+          <t>100347</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74407</t>
+          <t>92388</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113322</t>
+          <t>106139</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>196940</t>
+          <t>190033</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>166798</t>
+          <t>166960</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>210772</t>
+          <t>202648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>82,05%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>40754</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>30580</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>53379</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,23%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,93%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,56%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>30044</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>21634</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>39346</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>15,85%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,42%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,76%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>45192</t>
+          <t>30638</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33944</t>
+          <t>22891</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57464</t>
+          <t>40552</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>75236</t>
+          <t>71392</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61432</t>
+          <t>58797</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91757</t>
+          <t>85478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>195836</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>183211</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>206010</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>82,77%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77,44%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>87,07%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>159469</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>150167</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>167879</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>84,15%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,24%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>88,58%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>209136</t>
+          <t>152699</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>196864</t>
+          <t>142785</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>220384</t>
+          <t>160446</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>368605</t>
+          <t>348535</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>352084</t>
+          <t>334449</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>382409</t>
+          <t>361130</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,0%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>236590</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>236590</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>236590</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>254328</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>254328</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>254328</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>443841</t>
+          <t>419927</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>443841</t>
+          <t>419927</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>443841</t>
+          <t>419927</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21599</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13935</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>35112</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12,83%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,28%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20,86%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7696</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3595</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13493</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22554</t>
+          <t>7266</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13939</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35972</t>
+          <t>12968</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>30250</t>
+          <t>28865</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21066</t>
+          <t>19865</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47643</t>
+          <t>43135</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>146742</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>133229</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>154406</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,17%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>79,14%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,72%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>182705</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>176908</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>186806</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,91%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>162732</t>
+          <t>149784</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149314</t>
+          <t>144082</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>171347</t>
+          <t>153056</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>345437</t>
+          <t>296526</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>328044</t>
+          <t>282256</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>354621</t>
+          <t>305526</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>45346</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>36119</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>56150</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>26,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>21,45%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>33,34%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>49121</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>38858</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>59611</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>29,25%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>23,13%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>35,49%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48387</t>
+          <t>48231</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38058</t>
+          <t>38731</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60058</t>
+          <t>58277</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>97509</t>
+          <t>93577</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84547</t>
+          <t>80708</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114585</t>
+          <t>109002</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,48%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>123073</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>112269</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>132300</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>73,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>66,66%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>78,55%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>118841</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>108351</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>129104</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>70,75%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>64,51%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>76,87%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>131908</t>
+          <t>118914</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>120237</t>
+          <t>108868</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>142237</t>
+          <t>128414</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>250748</t>
+          <t>241987</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>233672</t>
+          <t>226562</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>263710</t>
+          <t>254856</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,95%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>348257</t>
+          <t>335564</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>348257</t>
+          <t>335564</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>348257</t>
+          <t>335564</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>143920</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>123615</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>172157</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>20,58%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>17,68%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>24,62%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>107431</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>89346</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>126675</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>16,15%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>13,43%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>19,04%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>156315</t>
+          <t>106858</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>134546</t>
+          <t>92798</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189991</t>
+          <t>123777</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>263747</t>
+          <t>250778</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>232576</t>
+          <t>224131</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>300917</t>
+          <t>282524</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>555336</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>527099</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>575641</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>79,42%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>75,38%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>82,32%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>788</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>557725</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>538481</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>575810</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>83,85%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>80,96%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>86,57%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>604007</t>
+          <t>521745</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>570331</t>
+          <t>504826</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>625776</t>
+          <t>535805</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1161730</t>
+          <t>1077081</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1124560</t>
+          <t>1045335</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1192901</t>
+          <t>1103728</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,12%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
